--- a/MAJSushiConfig/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMObservation.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMObservation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservation</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMEntry|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMEntry|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -266,7 +266,7 @@
     <t>FRLMObservation.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatient
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient
 </t>
   </si>
   <si>
@@ -301,7 +301,7 @@
     <t>FRLMObservation.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
 </t>
   </si>
   <si>
@@ -314,7 +314,7 @@
     <t>FRLMObservation.header.author[x].authorOrganisation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation
 </t>
   </si>
   <si>
@@ -327,7 +327,7 @@
     <t>FRLMObservation.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDevice
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevice
 </t>
   </si>
   <si>
@@ -340,8 +340,8 @@
     <t>FRLMObservation.header.performer[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -389,7 +389,7 @@
     <t>FRLMObservation.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMInformant
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMInformant
 </t>
   </si>
   <si>
@@ -451,8 +451,8 @@
     <t>FRLMObservation.header.directSubject[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatient
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDevicehttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessionalhttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisationhttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMProcedure</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevicehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessionalhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMProcedure</t>
   </si>
   <si>
     <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
@@ -499,7 +499,7 @@
     <t>FRLMObservation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMSpecimen
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSpecimen
 </t>
   </si>
   <si>
@@ -509,7 +509,7 @@
     <t>FRLMObservation.order</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMServiceRequest
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMServiceRequest
 </t>
   </si>
   <si>
@@ -519,7 +519,7 @@
     <t>FRLMObservation.bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMBodyStructure
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMBodyStructure
 </t>
   </si>
   <si>
@@ -640,8 +640,8 @@
     <t>FRLMObservation.derivedFrom[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMObservation
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMLaboratoryObservationhttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMImagingStudy</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservation
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMLaboratoryObservationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMImagingStudy</t>
   </si>
   <si>
     <t>Référence de la resource à partir de laquelle l'observation a été faite. Par exemple, une image échographique à partir de laquelle une mesure fœtale est réalisée.</t>
@@ -650,8 +650,8 @@
     <t>FRLMObservation.hasMember[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMLaboratoryObservation
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMObservation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMLaboratoryObservation
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservation</t>
   </si>
   <si>
     <t>Cette observation est un groupe d'observations (par exemple, une batterie de tests, un ensemble de mesures de signes vitaux).</t>

--- a/MAJSushiConfig/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
